--- a/outputs_xlsx_solution/prog-loop.4-wide-NC-1.xlsx
+++ b/outputs_xlsx_solution/prog-loop.4-wide-NC-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>IS</t>
   </si>
   <si>
@@ -135,6 +138,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -624,7 +630,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -644,13 +650,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -673,10 +679,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -696,16 +702,16 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -725,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -740,7 +746,7 @@
         <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +766,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
         <v>14</v>
@@ -801,7 +807,7 @@
         <v>14</v>
       </c>
       <c r="O8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -821,13 +827,19 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O9" t="s">
         <v>15</v>
       </c>
+      <c r="P9" t="s">
+        <v>15</v>
+      </c>
       <c r="Q9" t="s">
         <v>14</v>
       </c>
       <c r="R9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +850,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -850,10 +862,10 @@
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -864,7 +876,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -873,16 +885,16 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -893,7 +905,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -902,16 +914,16 @@
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -931,16 +943,16 @@
         <v>9</v>
       </c>
       <c r="L13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M13" t="s">
         <v>14</v>
       </c>
       <c r="N13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -960,7 +972,7 @@
         <v>9</v>
       </c>
       <c r="L14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N14" t="s">
         <v>14</v>
@@ -975,10 +987,10 @@
         <v>14</v>
       </c>
       <c r="R14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -998,16 +1010,19 @@
         <v>9</v>
       </c>
       <c r="L15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" t="s">
         <v>15</v>
       </c>
       <c r="N15" t="s">
         <v>14</v>
       </c>
       <c r="O15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -1027,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R16" t="s">
         <v>14</v>
@@ -1039,10 +1054,10 @@
         <v>14</v>
       </c>
       <c r="U16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -1062,16 +1077,16 @@
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U17" t="s">
         <v>14</v>
       </c>
       <c r="V17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -1082,7 +1097,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -1091,16 +1106,16 @@
         <v>9</v>
       </c>
       <c r="M18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N18" t="s">
         <v>14</v>
       </c>
       <c r="O18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1111,7 +1126,7 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -1120,16 +1135,19 @@
         <v>9</v>
       </c>
       <c r="M19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" t="s">
         <v>15</v>
       </c>
       <c r="O19" t="s">
         <v>14</v>
       </c>
       <c r="P19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -1140,7 +1158,7 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -1149,16 +1167,16 @@
         <v>9</v>
       </c>
       <c r="M20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O20" t="s">
         <v>14</v>
       </c>
       <c r="P20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -1178,16 +1196,16 @@
         <v>9</v>
       </c>
       <c r="N21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O21" t="s">
         <v>14</v>
       </c>
       <c r="P21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1207,8 +1225,14 @@
         <v>9</v>
       </c>
       <c r="N22" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" t="s">
         <v>15</v>
       </c>
+      <c r="Q22" t="s">
+        <v>15</v>
+      </c>
       <c r="R22" t="s">
         <v>14</v>
       </c>
@@ -1222,10 +1246,10 @@
         <v>14</v>
       </c>
       <c r="V22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1245,19 +1269,19 @@
         <v>9</v>
       </c>
       <c r="N23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P23" t="s">
         <v>14</v>
       </c>
       <c r="Q23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1277,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="O24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V24" t="s">
         <v>14</v>
@@ -1289,10 +1313,10 @@
         <v>14</v>
       </c>
       <c r="Y24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1312,25 +1336,25 @@
         <v>9</v>
       </c>
       <c r="O25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="s">
         <v>14</v>
       </c>
       <c r="Z25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -1341,7 +1365,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M26" t="s">
         <v>5</v>
@@ -1350,19 +1374,19 @@
         <v>9</v>
       </c>
       <c r="R26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T26" t="s">
         <v>14</v>
       </c>
       <c r="U26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -1373,7 +1397,7 @@
         <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M27" t="s">
         <v>5</v>
@@ -1382,19 +1406,19 @@
         <v>9</v>
       </c>
       <c r="S27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U27" t="s">
         <v>14</v>
       </c>
       <c r="V27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -1405,7 +1429,7 @@
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M28" t="s">
         <v>5</v>
@@ -1414,24 +1438,24 @@
         <v>9</v>
       </c>
       <c r="T28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V28" t="s">
         <v>14</v>
       </c>
       <c r="W28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
@@ -1439,7 +1463,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -1447,15 +1471,15 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -1463,39 +1487,55 @@
         <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" t="s">
         <v>32</v>
       </c>
-      <c r="B38" t="s">
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
         <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
